--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -76,6 +76,9 @@
     <t>Prefab/Coin</t>
   </si>
   <si>
+    <t>Item/Coin[cion-_0]</t>
+  </si>
+  <si>
     <t>item_potion_01</t>
   </si>
   <si>
@@ -100,6 +103,9 @@
     <t>dropitem</t>
   </si>
   <si>
+    <t>Item/Cactuslime[dropitem1-_1]</t>
+  </si>
+  <si>
     <t>item_cactuslime_needle_01</t>
   </si>
   <si>
@@ -107,6 +113,9 @@
   </si>
   <si>
     <t>따갑다.</t>
+  </si>
+  <si>
+    <t>Item/Cactuslime[dropitem1-_0]</t>
   </si>
 </sst>
 </file>
@@ -181,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -189,7 +198,7 @@
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -202,9 +211,6 @@
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -586,7 +592,9 @@
       <c r="G4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -608,16 +616,16 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3">
         <v>99.0</v>
@@ -647,26 +655,28 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="8">
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3">
         <v>999.0</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="3">
         <v>1.0</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -687,26 +697,28 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="8">
+      <c r="E7" s="3">
         <v>999.0</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="3">
         <v>20.0</v>
       </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -117,6 +117,30 @@
   <si>
     <t>Item/Cactuslime[dropitem1-_0]</t>
   </si>
+  <si>
+    <t>item_cowbombie_hat_01</t>
+  </si>
+  <si>
+    <t>좀비 모자</t>
+  </si>
+  <si>
+    <t>낡았다.</t>
+  </si>
+  <si>
+    <t>Item/Cowbombie[cowbombiedrop_0]</t>
+  </si>
+  <si>
+    <t>item_cowbombie_badge_01</t>
+  </si>
+  <si>
+    <t>보안관 뱃지</t>
+  </si>
+  <si>
+    <t>녹슬었다.</t>
+  </si>
+  <si>
+    <t>Item/Cowbombie[cowbombiedrop_1]</t>
+  </si>
 </sst>
 </file>
 
@@ -190,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -214,6 +238,9 @@
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,13 +460,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.0"/>
-    <col customWidth="1" min="2" max="2" width="17.13"/>
-    <col customWidth="1" min="3" max="3" width="44.38"/>
+    <col customWidth="1" min="1" max="1" width="23.63"/>
+    <col customWidth="1" min="2" max="2" width="19.13"/>
+    <col customWidth="1" min="3" max="3" width="29.13"/>
     <col customWidth="1" min="4" max="4" width="17.75"/>
     <col customWidth="1" min="5" max="5" width="26.75"/>
     <col customWidth="1" min="6" max="6" width="23.25"/>
-    <col customWidth="1" min="7" max="26" width="11.0"/>
+    <col customWidth="1" min="7" max="7" width="11.0"/>
+    <col customWidth="1" min="8" max="8" width="29.0"/>
+    <col customWidth="1" min="9" max="26" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -739,14 +768,28 @@
       <c r="Z7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="A8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="7">
+        <v>999.0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1.0</v>
+      </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -767,14 +810,28 @@
       <c r="Z8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="A9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="7">
+        <v>999.0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>25.0</v>
+      </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -799,7 +856,6 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -91,6 +91,33 @@
     <t>potion</t>
   </si>
   <si>
+    <t>Item/Potion[potion_2]</t>
+  </si>
+  <si>
+    <t>item_potion_02</t>
+  </si>
+  <si>
+    <t>자석 포션</t>
+  </si>
+  <si>
+    <t>주변 아이템을 끌어당기는 물약</t>
+  </si>
+  <si>
+    <t>Item/Potion[potion_6]</t>
+  </si>
+  <si>
+    <t>item_potion_03</t>
+  </si>
+  <si>
+    <t>공속 포션</t>
+  </si>
+  <si>
+    <t>순간적으로 공격속도를 올리는 포션</t>
+  </si>
+  <si>
+    <t>Item/Potion[potion_5]</t>
+  </si>
+  <si>
     <t>item_cactuslime_slime_01</t>
   </si>
   <si>
@@ -146,7 +173,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -172,6 +199,11 @@
       <sz val="11.0"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -214,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -241,6 +273,9 @@
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -621,7 +656,7 @@
       <c r="G4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="3"/>
@@ -663,7 +698,9 @@
         <v>5.0</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="H5" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -684,23 +721,23 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="3">
-        <v>999.0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1.0</v>
+      <c r="D6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="7">
+        <v>99.0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>10.0</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="7" t="s">
@@ -726,23 +763,23 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="3">
-        <v>999.0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>20.0</v>
+      <c r="D7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="7">
+        <v>99.0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>10.0</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="7" t="s">
@@ -768,27 +805,27 @@
       <c r="Z7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="7">
+      <c r="D8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="3">
         <v>999.0</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="3">
         <v>1.0</v>
       </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="7" t="s">
-        <v>38</v>
+      <c r="H8" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -810,27 +847,27 @@
       <c r="Z8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="C9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="3">
         <v>999.0</v>
       </c>
-      <c r="F9" s="7">
-        <v>25.0</v>
+      <c r="F9" s="3">
+        <v>20.0</v>
       </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="7" t="s">
-        <v>42</v>
+      <c r="H9" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -852,13 +889,28 @@
       <c r="Z9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="A10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="3">
+        <v>999.0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1.0</v>
+      </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -879,14 +931,28 @@
       <c r="Z10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="3">
+        <v>999.0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>25.0</v>
+      </c>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -911,7 +977,6 @@
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -1019,9 +1084,9 @@
       <c r="Z15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1047,9 +1112,9 @@
       <c r="Z16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -6758,8 +6823,62 @@
       <c r="Y220" s="3"/>
       <c r="Z220" s="3"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1">
+      <c r="A221" s="3"/>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="3"/>
+      <c r="E221" s="3"/>
+      <c r="F221" s="3"/>
+      <c r="G221" s="3"/>
+      <c r="H221" s="3"/>
+      <c r="I221" s="3"/>
+      <c r="J221" s="3"/>
+      <c r="K221" s="3"/>
+      <c r="L221" s="3"/>
+      <c r="M221" s="3"/>
+      <c r="N221" s="3"/>
+      <c r="O221" s="3"/>
+      <c r="P221" s="3"/>
+      <c r="Q221" s="3"/>
+      <c r="R221" s="3"/>
+      <c r="S221" s="3"/>
+      <c r="T221" s="3"/>
+      <c r="U221" s="3"/>
+      <c r="V221" s="3"/>
+      <c r="W221" s="3"/>
+      <c r="X221" s="3"/>
+      <c r="Y221" s="3"/>
+      <c r="Z221" s="3"/>
+    </row>
+    <row r="222" ht="15.75" customHeight="1">
+      <c r="A222" s="3"/>
+      <c r="B222" s="3"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
+      <c r="E222" s="3"/>
+      <c r="F222" s="3"/>
+      <c r="G222" s="3"/>
+      <c r="H222" s="3"/>
+      <c r="I222" s="3"/>
+      <c r="J222" s="3"/>
+      <c r="K222" s="3"/>
+      <c r="L222" s="3"/>
+      <c r="M222" s="3"/>
+      <c r="N222" s="3"/>
+      <c r="O222" s="3"/>
+      <c r="P222" s="3"/>
+      <c r="Q222" s="3"/>
+      <c r="R222" s="3"/>
+      <c r="S222" s="3"/>
+      <c r="T222" s="3"/>
+      <c r="U222" s="3"/>
+      <c r="V222" s="3"/>
+      <c r="W222" s="3"/>
+      <c r="X222" s="3"/>
+      <c r="Y222" s="3"/>
+      <c r="Z222" s="3"/>
+    </row>
     <row r="223" ht="15.75" customHeight="1"/>
     <row r="224" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
@@ -7538,6 +7657,8 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.699999988079071" right="0.699999988079071" top="0.75"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -31,6 +31,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>ItemType</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -43,7 +46,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ItemType</t>
+    <t>EItemType</t>
   </si>
   <si>
     <t>MaxStackCount</t>
@@ -70,9 +73,6 @@
     <t>돈이다.</t>
   </si>
   <si>
-    <t>coin</t>
-  </si>
-  <si>
     <t>Prefab/Coin</t>
   </si>
   <si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>체력을 회복하는 물약.</t>
-  </si>
-  <si>
-    <t>potion</t>
   </si>
   <si>
     <t>Item/Potion[potion_2]</t>
@@ -125,9 +122,6 @@
   </si>
   <si>
     <t>끈적하다.</t>
-  </si>
-  <si>
-    <t>dropitem</t>
   </si>
   <si>
     <t>Item/Cactuslime[dropitem1-_1]</t>
@@ -203,7 +197,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -246,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -259,24 +252,25 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -552,14 +546,14 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>5</v>
@@ -589,68 +583,68 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
+      <c r="I3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3" t="s">
         <v>19</v>
+      </c>
+      <c r="D4" s="8">
+        <v>2.0</v>
       </c>
       <c r="E4" s="3">
         <v>99999.0</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="9">
         <v>1.0</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -688,8 +682,8 @@
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
+      <c r="D5" s="8">
+        <v>3.0</v>
       </c>
       <c r="E5" s="3">
         <v>99.0</v>
@@ -698,8 +692,8 @@
         <v>5.0</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="7" t="s">
-        <v>26</v>
+      <c r="H5" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -721,27 +715,27 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8">
+        <v>4.0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>99.0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="7">
-        <v>99.0</v>
-      </c>
-      <c r="F6" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -763,27 +757,27 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>99.0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="7">
-        <v>99.0</v>
-      </c>
-      <c r="F7" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -806,16 +800,16 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>38</v>
+      <c r="D8" s="8">
+        <v>1.0</v>
       </c>
       <c r="E8" s="3">
         <v>999.0</v>
@@ -825,7 +819,7 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -848,16 +842,16 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>38</v>
+      <c r="D9" s="8">
+        <v>1.0</v>
       </c>
       <c r="E9" s="3">
         <v>999.0</v>
@@ -867,7 +861,7 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -890,16 +884,16 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>38</v>
+      <c r="D10" s="8">
+        <v>1.0</v>
       </c>
       <c r="E10" s="3">
         <v>999.0</v>
@@ -909,7 +903,7 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -932,16 +926,16 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>38</v>
+      <c r="D11" s="8">
+        <v>1.0</v>
       </c>
       <c r="E11" s="3">
         <v>999.0</v>
@@ -951,7 +945,7 @@
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -6823,62 +6817,8 @@
       <c r="Y220" s="3"/>
       <c r="Z220" s="3"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="3"/>
-      <c r="B221" s="3"/>
-      <c r="C221" s="3"/>
-      <c r="D221" s="3"/>
-      <c r="E221" s="3"/>
-      <c r="F221" s="3"/>
-      <c r="G221" s="3"/>
-      <c r="H221" s="3"/>
-      <c r="I221" s="3"/>
-      <c r="J221" s="3"/>
-      <c r="K221" s="3"/>
-      <c r="L221" s="3"/>
-      <c r="M221" s="3"/>
-      <c r="N221" s="3"/>
-      <c r="O221" s="3"/>
-      <c r="P221" s="3"/>
-      <c r="Q221" s="3"/>
-      <c r="R221" s="3"/>
-      <c r="S221" s="3"/>
-      <c r="T221" s="3"/>
-      <c r="U221" s="3"/>
-      <c r="V221" s="3"/>
-      <c r="W221" s="3"/>
-      <c r="X221" s="3"/>
-      <c r="Y221" s="3"/>
-      <c r="Z221" s="3"/>
-    </row>
-    <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="3"/>
-      <c r="B222" s="3"/>
-      <c r="C222" s="3"/>
-      <c r="D222" s="3"/>
-      <c r="E222" s="3"/>
-      <c r="F222" s="3"/>
-      <c r="G222" s="3"/>
-      <c r="H222" s="3"/>
-      <c r="I222" s="3"/>
-      <c r="J222" s="3"/>
-      <c r="K222" s="3"/>
-      <c r="L222" s="3"/>
-      <c r="M222" s="3"/>
-      <c r="N222" s="3"/>
-      <c r="O222" s="3"/>
-      <c r="P222" s="3"/>
-      <c r="Q222" s="3"/>
-      <c r="R222" s="3"/>
-      <c r="S222" s="3"/>
-      <c r="T222" s="3"/>
-      <c r="U222" s="3"/>
-      <c r="V222" s="3"/>
-      <c r="W222" s="3"/>
-      <c r="X222" s="3"/>
-      <c r="Y222" s="3"/>
-      <c r="Z222" s="3"/>
-    </row>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
     <row r="223" ht="15.75" customHeight="1"/>
     <row r="224" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
@@ -7657,8 +7597,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.699999988079071" right="0.699999988079071" top="0.75"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>bool</t>
   </si>
   <si>
     <t>Id</t>
@@ -62,6 +65,9 @@
   </si>
   <si>
     <t>Grade</t>
+  </si>
+  <si>
+    <t>IsUseable</t>
   </si>
   <si>
     <t>item_coin_01</t>
@@ -167,7 +173,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -193,6 +199,12 @@
       <sz val="11.0"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color theme="1"/>
@@ -252,25 +264,25 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -546,7 +558,7 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -561,10 +573,12 @@
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="3"/>
+      <c r="J2" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
@@ -584,61 +598,63 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="H3" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="I3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
+        <v>17</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="8">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3">
         <v>2.0</v>
       </c>
       <c r="E4" s="3">
@@ -648,13 +664,15 @@
         <v>1.0</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="J4" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -674,15 +692,15 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="8">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3">
         <v>3.0</v>
       </c>
       <c r="E5" s="3">
@@ -693,10 +711,12 @@
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="J5" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -716,15 +736,15 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="8">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3">
         <v>4.0</v>
       </c>
       <c r="E6" s="3">
@@ -735,10 +755,12 @@
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="J6" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -758,15 +780,15 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="8">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3">
         <v>5.0</v>
       </c>
       <c r="E7" s="3">
@@ -777,10 +799,12 @@
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="J7" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -800,15 +824,15 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="8">
+        <v>38</v>
+      </c>
+      <c r="D8" s="3">
         <v>1.0</v>
       </c>
       <c r="E8" s="3">
@@ -819,10 +843,12 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="J8" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -842,15 +868,15 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="8">
+        <v>42</v>
+      </c>
+      <c r="D9" s="3">
         <v>1.0</v>
       </c>
       <c r="E9" s="3">
@@ -861,10 +887,12 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="J9" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -884,15 +912,15 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="8">
+        <v>46</v>
+      </c>
+      <c r="D10" s="3">
         <v>1.0</v>
       </c>
       <c r="E10" s="3">
@@ -903,10 +931,12 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="J10" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -926,15 +956,15 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="8">
+        <v>50</v>
+      </c>
+      <c r="D11" s="3">
         <v>1.0</v>
       </c>
       <c r="E11" s="3">
@@ -945,10 +975,12 @@
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="J11" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -168,12 +168,60 @@
   <si>
     <t>Item/Cowbombie[cowbombiedrop_1]</t>
   </si>
+  <si>
+    <t>item_maxikeleton_hat_01</t>
+  </si>
+  <si>
+    <t>스켈레톤 모자</t>
+  </si>
+  <si>
+    <t>화려하다.</t>
+  </si>
+  <si>
+    <t>Item/skeleton[skeletondrop_0]</t>
+  </si>
+  <si>
+    <t>item_maxikeleton_guitar_01</t>
+  </si>
+  <si>
+    <t>기타</t>
+  </si>
+  <si>
+    <t>흥겹다.</t>
+  </si>
+  <si>
+    <t>Item/skeleton[skeletondrop_1]</t>
+  </si>
+  <si>
+    <t>item_deserteagle_feather_01</t>
+  </si>
+  <si>
+    <t>깃털</t>
+  </si>
+  <si>
+    <t>간지럽다.</t>
+  </si>
+  <si>
+    <t>Item/eagle[eagledropp_0]</t>
+  </si>
+  <si>
+    <t>item_deserteagle_diamond_01</t>
+  </si>
+  <si>
+    <t>다이아몬드</t>
+  </si>
+  <si>
+    <t>빛난다.</t>
+  </si>
+  <si>
+    <t>Item/eagle[eagledropp_2]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -209,6 +257,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -251,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -264,9 +317,6 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
@@ -274,15 +324,21 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -573,10 +629,10 @@
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K2" s="3"/>
@@ -597,52 +653,52 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -660,7 +716,7 @@
       <c r="E4" s="3">
         <v>99999.0</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="7">
         <v>1.0</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -670,7 +726,7 @@
         <v>23</v>
       </c>
       <c r="I4" s="3"/>
-      <c r="J4" s="4" t="b">
+      <c r="J4" s="3" t="b">
         <v>0</v>
       </c>
       <c r="K4" s="3"/>
@@ -714,7 +770,7 @@
         <v>27</v>
       </c>
       <c r="I5" s="3"/>
-      <c r="J5" s="4" t="b">
+      <c r="J5" s="3" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="3"/>
@@ -758,7 +814,7 @@
         <v>31</v>
       </c>
       <c r="I6" s="3"/>
-      <c r="J6" s="4" t="b">
+      <c r="J6" s="3" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="3"/>
@@ -782,7 +838,7 @@
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -802,7 +858,7 @@
         <v>35</v>
       </c>
       <c r="I7" s="3"/>
-      <c r="J7" s="4" t="b">
+      <c r="J7" s="3" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="3"/>
@@ -846,7 +902,7 @@
         <v>39</v>
       </c>
       <c r="I8" s="3"/>
-      <c r="J8" s="4" t="b">
+      <c r="J8" s="3" t="b">
         <v>0</v>
       </c>
       <c r="K8" s="3"/>
@@ -890,7 +946,7 @@
         <v>43</v>
       </c>
       <c r="I9" s="3"/>
-      <c r="J9" s="4" t="b">
+      <c r="J9" s="3" t="b">
         <v>0</v>
       </c>
       <c r="K9" s="3"/>
@@ -934,7 +990,7 @@
         <v>47</v>
       </c>
       <c r="I10" s="3"/>
-      <c r="J10" s="4" t="b">
+      <c r="J10" s="3" t="b">
         <v>0</v>
       </c>
       <c r="K10" s="3"/>
@@ -978,7 +1034,7 @@
         <v>51</v>
       </c>
       <c r="I11" s="3"/>
-      <c r="J11" s="4" t="b">
+      <c r="J11" s="3" t="b">
         <v>0</v>
       </c>
       <c r="K11" s="3"/>
@@ -999,15 +1055,32 @@
       <c r="Z11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="11">
+        <v>999.0</v>
+      </c>
+      <c r="F12" s="10">
+        <v>2.0</v>
+      </c>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="J12" s="10" t="b">
+        <v>0</v>
+      </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -1026,16 +1099,32 @@
       <c r="Z12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="10">
+        <v>999.0</v>
+      </c>
+      <c r="F13" s="10">
+        <v>40.0</v>
+      </c>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="J13" s="10" t="b">
+        <v>0</v>
+      </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -1054,16 +1143,32 @@
       <c r="Z13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="A14" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="E14" s="10">
+        <v>999.0</v>
+      </c>
+      <c r="F14" s="10">
+        <v>2.0</v>
+      </c>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="J14" s="10" t="b">
+        <v>0</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -1082,16 +1187,32 @@
       <c r="Z14" s="3"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="A15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="10">
+        <v>999.0</v>
+      </c>
+      <c r="F15" s="10">
+        <v>50.0</v>
+      </c>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="J15" s="10" t="b">
+        <v>0</v>
+      </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="80">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -103,7 +103,7 @@
     <t>자석 포션</t>
   </si>
   <si>
-    <t>주변 아이템을 끌어당기는 물약</t>
+    <t>주변 아이템을 끌어당기는 물약.</t>
   </si>
   <si>
     <t>Item/Potion[potion_6]</t>
@@ -115,7 +115,7 @@
     <t>공속 포션</t>
   </si>
   <si>
-    <t>순간적으로 공격속도를 올리는 포션</t>
+    <t>순간적으로 공격속도를 올리는 물약.</t>
   </si>
   <si>
     <t>Item/Potion[potion_5]</t>
@@ -215,13 +215,49 @@
   </si>
   <si>
     <t>Item/eagle[eagledropp_2]</t>
+  </si>
+  <si>
+    <t>item_boss_branch_01</t>
+  </si>
+  <si>
+    <t>나뭇가지</t>
+  </si>
+  <si>
+    <t>잘 부러진다.</t>
+  </si>
+  <si>
+    <t>item/bossdrop[bossdrop__0]</t>
+  </si>
+  <si>
+    <t>item_boss_essence_01</t>
+  </si>
+  <si>
+    <t>정수</t>
+  </si>
+  <si>
+    <t>이상한 기운이 감돈다.</t>
+  </si>
+  <si>
+    <t>item/bossdrop[bossdrop__1]</t>
+  </si>
+  <si>
+    <t>item_coin_02</t>
+  </si>
+  <si>
+    <t>동전주머니</t>
+  </si>
+  <si>
+    <t>큰 돈이다.</t>
+  </si>
+  <si>
+    <t>Item/Coin[cion-_8]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -257,11 +293,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -304,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -329,15 +360,12 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -797,7 +825,7 @@
       <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="8" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="3">
@@ -838,10 +866,10 @@
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="8" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="3">
@@ -1055,30 +1083,30 @@
       <c r="Z11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="3">
         <v>1.0</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <v>999.0</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="3">
         <v>2.0</v>
       </c>
       <c r="G12" s="3"/>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I12" s="3"/>
-      <c r="J12" s="10" t="b">
+      <c r="J12" s="3" t="b">
         <v>0</v>
       </c>
       <c r="K12" s="3"/>
@@ -1099,30 +1127,30 @@
       <c r="Z12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="3">
         <v>1.0</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="3">
         <v>999.0</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="3">
         <v>40.0</v>
       </c>
       <c r="G13" s="3"/>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="3" t="s">
         <v>59</v>
       </c>
       <c r="I13" s="3"/>
-      <c r="J13" s="10" t="b">
+      <c r="J13" s="3" t="b">
         <v>0</v>
       </c>
       <c r="K13" s="3"/>
@@ -1143,30 +1171,30 @@
       <c r="Z13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="3">
         <v>1.0</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="3">
         <v>999.0</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="3">
         <v>2.0</v>
       </c>
       <c r="G14" s="3"/>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="3" t="s">
         <v>63</v>
       </c>
       <c r="I14" s="3"/>
-      <c r="J14" s="10" t="b">
+      <c r="J14" s="3" t="b">
         <v>0</v>
       </c>
       <c r="K14" s="3"/>
@@ -1187,30 +1215,30 @@
       <c r="Z14" s="3"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="3">
         <v>1.0</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="3">
         <v>999.0</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="3">
         <v>50.0</v>
       </c>
       <c r="G15" s="3"/>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="3" t="s">
         <v>67</v>
       </c>
       <c r="I15" s="3"/>
-      <c r="J15" s="10" t="b">
+      <c r="J15" s="3" t="b">
         <v>0</v>
       </c>
       <c r="K15" s="3"/>
@@ -1231,16 +1259,32 @@
       <c r="Z15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="A16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="10">
+        <v>999.0</v>
+      </c>
+      <c r="F16" s="10">
+        <v>20.0</v>
+      </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="10" t="b">
+        <v>0</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -1259,16 +1303,32 @@
       <c r="Z16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="A17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="E17" s="10">
+        <v>999.0</v>
+      </c>
+      <c r="F17" s="10">
+        <v>300.0</v>
+      </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="10" t="s">
+        <v>75</v>
+      </c>
       <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="J17" s="10" t="b">
+        <v>0</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -1287,16 +1347,32 @@
       <c r="Z17" s="3"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="A18" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="E18" s="10">
+        <v>9999999.0</v>
+      </c>
+      <c r="F18" s="10">
+        <v>1000.0</v>
+      </c>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="J18" s="10" t="b">
+        <v>0</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
